--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.85854824841894</v>
+        <v>5.014514090368078</v>
       </c>
       <c r="D2" t="n">
-        <v>28.54872832885364</v>
+        <v>4.639168353438717</v>
       </c>
       <c r="E2" t="n">
-        <v>9.950604801346165</v>
+        <v>1.616973280218752</v>
       </c>
       <c r="F2" t="n">
-        <v>6.533739874570672</v>
+        <v>1.061732729617734</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.84361000236259</v>
+        <v>3.549586625383921</v>
       </c>
       <c r="D3" t="n">
-        <v>24.47358770757919</v>
+        <v>3.976958002481618</v>
       </c>
       <c r="E3" t="n">
-        <v>9.950604801346165</v>
+        <v>1.616973280218752</v>
       </c>
       <c r="F3" t="n">
-        <v>6.533739874570672</v>
+        <v>1.061732729617734</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.632088208889508</v>
+        <v>1.565214333944545</v>
       </c>
       <c r="D4" t="n">
-        <v>7.242589634687701</v>
+        <v>1.176920815636751</v>
       </c>
       <c r="E4" t="n">
-        <v>9.950604801346165</v>
+        <v>1.616973280218752</v>
       </c>
       <c r="F4" t="n">
-        <v>6.533739874570672</v>
+        <v>1.061732729617734</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.92095612178538</v>
+        <v>4.537155369790124</v>
       </c>
       <c r="D5" t="n">
-        <v>28.70348083856597</v>
+        <v>4.66431563626697</v>
       </c>
       <c r="E5" t="n">
-        <v>9.950604801346165</v>
+        <v>1.616973280218752</v>
       </c>
       <c r="F5" t="n">
-        <v>6.533739874570672</v>
+        <v>1.061732729617734</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.23820229487373</v>
+        <v>2.151207872916981</v>
       </c>
       <c r="D6" t="n">
-        <v>12.64385088118337</v>
+        <v>2.054625768192298</v>
       </c>
       <c r="E6" t="n">
-        <v>9.950604801346165</v>
+        <v>1.616973280218752</v>
       </c>
       <c r="F6" t="n">
-        <v>6.533739874570672</v>
+        <v>1.061732729617734</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.90136775272421</v>
+        <v>5.346472259817683</v>
       </c>
       <c r="D7" t="n">
-        <v>23.32810104656902</v>
+        <v>3.790816420067466</v>
       </c>
       <c r="E7" t="n">
-        <v>9.950604801346165</v>
+        <v>1.616973280218752</v>
       </c>
       <c r="F7" t="n">
-        <v>6.533739874570672</v>
+        <v>1.061732729617734</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.04843641004855</v>
+        <v>1.47037091663289</v>
       </c>
       <c r="D8" t="n">
-        <v>23.4133806064861</v>
+        <v>3.804674348553991</v>
       </c>
       <c r="E8" t="n">
-        <v>9.950604801346165</v>
+        <v>1.616973280218752</v>
       </c>
       <c r="F8" t="n">
-        <v>6.533739874570672</v>
+        <v>1.061732729617734</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.71511950137164</v>
+        <v>5.966206918972891</v>
       </c>
       <c r="D9" t="n">
-        <v>23.58903818898428</v>
+        <v>3.833218705709946</v>
       </c>
       <c r="E9" t="n">
-        <v>9.950604801346165</v>
+        <v>1.616973280218752</v>
       </c>
       <c r="F9" t="n">
-        <v>6.533739874570672</v>
+        <v>1.061732729617734</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.51844342577367</v>
+        <v>3.009247056688221</v>
       </c>
       <c r="D10" t="n">
-        <v>18.964440408301</v>
+        <v>3.081721566348913</v>
       </c>
       <c r="E10" t="n">
-        <v>9.950604801346165</v>
+        <v>1.616973280218752</v>
       </c>
       <c r="F10" t="n">
-        <v>6.533739874570672</v>
+        <v>1.061732729617734</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.88669887965363</v>
+        <v>6.644088567943715</v>
       </c>
       <c r="D11" t="n">
-        <v>11.55568384219163</v>
+        <v>1.877798624356141</v>
       </c>
       <c r="E11" t="n">
-        <v>9.950604801346165</v>
+        <v>1.616973280218752</v>
       </c>
       <c r="F11" t="n">
-        <v>6.533739874570672</v>
+        <v>1.061732729617734</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.18544487267853</v>
+        <v>3.280134791810261</v>
       </c>
       <c r="D12" t="n">
-        <v>22.19234102117215</v>
+        <v>3.606255415940474</v>
       </c>
       <c r="E12" t="n">
-        <v>9.950604801346165</v>
+        <v>1.616973280218752</v>
       </c>
       <c r="F12" t="n">
-        <v>6.533739874570672</v>
+        <v>1.061732729617734</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>26.15445427855077</v>
+        <v>4.250098820264501</v>
       </c>
       <c r="D13" t="n">
-        <v>16.27882059609971</v>
+        <v>2.645308346866202</v>
       </c>
       <c r="E13" t="n">
-        <v>9.950604801346165</v>
+        <v>1.616973280218752</v>
       </c>
       <c r="F13" t="n">
-        <v>6.533739874570672</v>
+        <v>1.061732729617734</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
